--- a/TheNextPeak/TheNextPeak__March_results.xlsx
+++ b/TheNextPeak/TheNextPeak__March_results.xlsx
@@ -472,100 +472,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1265626</v>
+        <v>116218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BL13</t>
-        </is>
-      </c>
+          <t>Reidar Dahl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>199.467</v>
+        <v>420.161</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>139.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7078446</v>
+        <v>199053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ash.&amp;#127793;  Miles (ABR)</t>
+          <t>Trevor Connor (MGCC)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ABR Cycle Team</t>
+          <t>MGCC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>225.328</v>
+        <v>241.356</v>
       </c>
       <c r="G3" t="n">
-        <v>25.86099999999999</v>
+        <v>5.317999999999984</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5070491</v>
+        <v>334292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Eugene Klitenik [B2C2]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>266.944</v>
+        <v>255.848</v>
       </c>
       <c r="G4" t="n">
-        <v>67.477</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,81 +566,81 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>684576</v>
+        <v>368051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Robbie Alunni</t>
+          <t>Andrew Speck BCC Astros</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Team Jane Fonda</t>
+          <t>BCC Astros</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>322.48</v>
+        <v>397.799</v>
       </c>
       <c r="G5" t="n">
-        <v>123.013</v>
+        <v>117.028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>990876</v>
+        <v>659633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pete Connor (TNP) </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Kris HSN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>236.038</v>
+        <v>287.815</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>27.38999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3081959</v>
+        <v>684576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jomar Bjorge</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Robbie Alunni</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Team Jane Fonda</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>241.333</v>
+        <v>322.48</v>
       </c>
       <c r="G7" t="n">
-        <v>5.294999999999987</v>
+        <v>123.013</v>
       </c>
     </row>
     <row r="8">
@@ -663,23 +655,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>199053</v>
+        <v>769731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Trevor Connor (MGCC)</t>
+          <t>Steve Burns (Sussex Revolution VC - B)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MGCC</t>
+          <t>SRVC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>241.356</v>
+        <v>290.585</v>
       </c>
       <c r="G8" t="n">
-        <v>5.317999999999984</v>
+        <v>54.54699999999997</v>
       </c>
     </row>
     <row r="9">
@@ -694,73 +686,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>334292</v>
+        <v>990876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Eugene Klitenik [B2C2]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>255.848</v>
+        <v>236.038</v>
       </c>
       <c r="G9" t="n">
-        <v>19.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1654998</v>
+        <v>1151116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jean sebastien vaast</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Michael Tandy (RHINO)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>260.698</v>
+        <v>280.771</v>
       </c>
       <c r="G10" t="n">
-        <v>24.65999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2747647</v>
+        <v>1265626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Masahiko Uemura</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>264.829</v>
+        <v>199.467</v>
       </c>
       <c r="G11" t="n">
-        <v>28.791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -775,23 +779,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>769731</v>
+        <v>1281309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Steve Burns (Sussex Revolution VC - B)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SRVC</t>
-        </is>
-      </c>
+          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>290.585</v>
+        <v>373.381</v>
       </c>
       <c r="G12" t="n">
-        <v>54.54699999999997</v>
+        <v>137.343</v>
       </c>
     </row>
     <row r="13">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1281309</v>
+        <v>1654998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
+          <t>jean sebastien vaast</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>373.381</v>
+        <v>260.698</v>
       </c>
       <c r="G13" t="n">
-        <v>137.343</v>
+        <v>24.65999999999997</v>
       </c>
     </row>
     <row r="14">
@@ -864,73 +864,73 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3148216</v>
+        <v>2709880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hide  Kaz0[SIMONE]</t>
+          <t xml:space="preserve"> T C</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>260.888</v>
+        <v>298.541</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4629999999999654</v>
+        <v>38.11599999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>659633</v>
+        <v>2747647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kris HSN</t>
+          <t>Masahiko Uemura</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>287.815</v>
+        <v>264.829</v>
       </c>
       <c r="G16" t="n">
-        <v>27.38999999999999</v>
+        <v>28.791</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2709880</v>
+        <v>3081959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> T C</t>
+          <t>Jomar Bjorge</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>298.541</v>
+        <v>241.333</v>
       </c>
       <c r="G17" t="n">
-        <v>38.11599999999999</v>
+        <v>5.294999999999987</v>
       </c>
     </row>
     <row r="18">
@@ -945,56 +945,56 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6912866</v>
+        <v>3148216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cathy Drozd</t>
+          <t>Hide  Kaz0[SIMONE]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>302.218</v>
+        <v>260.888</v>
       </c>
       <c r="G18" t="n">
-        <v>41.79300000000001</v>
+        <v>0.4629999999999654</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1151116</v>
+        <v>5070491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Michael Tandy (RHINO)</t>
+          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>280.771</v>
+        <v>266.944</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>67.477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1003,50 +1003,50 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7675581</v>
+        <v>6912866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jesper Morsing</t>
+          <t>Cathy Drozd</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>326.363</v>
+        <v>302.218</v>
       </c>
       <c r="G20" t="n">
-        <v>45.59199999999998</v>
+        <v>41.79300000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>368051</v>
+        <v>7078446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Andrew Speck BCC Astros</t>
+          <t>Ash.&amp;#127793;  Miles (ABR)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BCC Astros</t>
+          <t>ABR Cycle Team</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>397.799</v>
+        <v>225.328</v>
       </c>
       <c r="G21" t="n">
-        <v>117.028</v>
+        <v>25.86099999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1057,23 +1057,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>116218</v>
+        <v>7675581</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reidar Dahl</t>
+          <t>Jesper Morsing</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>420.161</v>
+        <v>326.363</v>
       </c>
       <c r="G22" t="n">
-        <v>139.39</v>
+        <v>45.59199999999998</v>
       </c>
     </row>
     <row r="23">
@@ -1166,116 +1166,108 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1308320</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luke Osborne [RWB eSports] </t>
+          <t>Morten Andersen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>#EDDK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>479.937</v>
+        <v>487.635</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>7.697999999999979</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79179</v>
+        <v>88976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Morten Andersen</t>
+          <t>Thomas Lokar &amp;#128058;</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>#EDDK</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>487.635</v>
+        <v>571.562</v>
       </c>
       <c r="G3" t="n">
-        <v>7.697999999999979</v>
+        <v>35.48900000000003</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1457528</v>
+        <v>558924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>William [ghost]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
-        </is>
-      </c>
+          <t>Robert Mairs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>496.404</v>
+        <v>711.848</v>
       </c>
       <c r="G4" t="n">
-        <v>16.46699999999998</v>
+        <v>175.775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2344929</v>
+        <v>599299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mitchell Stewart</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BCC</t>
-        </is>
-      </c>
+          <t>luigi kristensen</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>502.271</v>
+        <v>600.14</v>
       </c>
       <c r="G5" t="n">
-        <v>22.334</v>
+        <v>64.06700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1286,116 +1278,112 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7317487</v>
+        <v>909259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B Goggin</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+          <t>Roland Nestler</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>504.309</v>
+        <v>541.193</v>
       </c>
       <c r="G6" t="n">
-        <v>24.37200000000001</v>
+        <v>61.25599999999997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2100487</v>
+        <v>922347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M Mike</t>
+          <t>YH. Tan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>[Ascenders]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>504.721</v>
+        <v>613.372</v>
       </c>
       <c r="G7" t="n">
-        <v>24.78399999999999</v>
+        <v>77.29899999999998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2149546</v>
+        <v>990876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F8" t="n">
-        <v>508.694</v>
+        <v>576.9349999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>28.75700000000001</v>
+        <v>88.11799999999994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1857344</v>
+        <v>1048743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Racing Ruub</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>The Watt Squad</t>
-        </is>
-      </c>
+          <t>Stephen Anderson</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>513.434</v>
+        <v>518.052</v>
       </c>
       <c r="G9" t="n">
-        <v>33.49699999999996</v>
+        <v>29.23500000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1406,27 +1394,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5238690</v>
+        <v>1308320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kjeld van der Lijke</t>
+          <t xml:space="preserve">Luke Osborne [RWB eSports] </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>532.005</v>
+        <v>479.937</v>
       </c>
       <c r="G10" t="n">
-        <v>52.06799999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1441,50 +1429,54 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7619023</v>
+        <v>1457528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Simone Batini</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>William [ghost]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>533.292</v>
+        <v>496.404</v>
       </c>
       <c r="G11" t="n">
-        <v>53.35500000000002</v>
+        <v>16.46699999999998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4390497</v>
+        <v>1627178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alex Hart (BL13)</t>
+          <t>Antonio Mateus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>PTz</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>537.454</v>
+        <v>519.272</v>
       </c>
       <c r="G12" t="n">
-        <v>57.51699999999994</v>
+        <v>30.45500000000004</v>
       </c>
     </row>
     <row r="13">
@@ -1495,139 +1487,147 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>909259</v>
+        <v>1857344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Roland Nestler</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Racing Ruub</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The Watt Squad</t>
+        </is>
+      </c>
       <c r="F13" t="n">
-        <v>541.193</v>
+        <v>513.434</v>
       </c>
       <c r="G13" t="n">
-        <v>61.25599999999997</v>
+        <v>33.49699999999996</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5070491</v>
+        <v>2026013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
+          <t>12059 Laura ADRIEN [3CY]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>3 Cycles [3CY]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>718.255</v>
+        <v>567.131</v>
       </c>
       <c r="G14" t="n">
-        <v>238.318</v>
+        <v>31.05799999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4500073</v>
+        <v>2100487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pieter de Meester</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>M Mike</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>488.817</v>
+        <v>504.721</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>24.78399999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2806376</v>
+        <v>2149546</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Daan Crombach</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ZweetZ</t>
-        </is>
-      </c>
+          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>512.711</v>
+        <v>508.694</v>
       </c>
       <c r="G16" t="n">
-        <v>23.89400000000001</v>
+        <v>28.75700000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1048743</v>
+        <v>2344929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stephen Anderson</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Mitchell Stewart</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BCC</t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>518.052</v>
+        <v>502.271</v>
       </c>
       <c r="G17" t="n">
-        <v>29.23500000000001</v>
+        <v>22.334</v>
       </c>
     </row>
     <row r="18">
@@ -1642,108 +1642,112 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1627178</v>
+        <v>2806376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Antonio Mateus</t>
+          <t>Daan Crombach</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PTz</t>
+          <t>ZweetZ</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>519.272</v>
+        <v>512.711</v>
       </c>
       <c r="G18" t="n">
-        <v>30.45500000000004</v>
+        <v>23.89400000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4705264</v>
+        <v>3937260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scott Houck</t>
+          <t>Addict Shigyo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>574.913</v>
+        <v>588.2910000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>86.096</v>
+        <v>52.21800000000007</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>990876</v>
+        <v>4177429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pete Connor (TNP) </t>
+          <t xml:space="preserve">F F </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>576.9349999999999</v>
+        <v>536.073</v>
       </c>
       <c r="G20" t="n">
-        <v>88.11799999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6973606</v>
+        <v>4390497</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ch NAKA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Alex Hart (BL13)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F21" t="n">
-        <v>577.187</v>
+        <v>537.454</v>
       </c>
       <c r="G21" t="n">
-        <v>88.37</v>
+        <v>57.51699999999994</v>
       </c>
     </row>
     <row r="22">
@@ -1754,47 +1758,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6166908</v>
+        <v>4500073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cory Gross</t>
+          <t>Pieter de Meester</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>577.551</v>
+        <v>488.817</v>
       </c>
       <c r="G22" t="n">
-        <v>88.73400000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4177429</v>
+        <v>4550173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
+          <t>Robert Kuramshin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>536.073</v>
+        <v>661.97</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1803,28 +1807,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7319731</v>
+        <v>4705264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ryan Baker</t>
+          <t>Scott Houck</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>566.95</v>
+        <v>574.913</v>
       </c>
       <c r="G24" t="n">
-        <v>30.87700000000007</v>
+        <v>86.096</v>
       </c>
     </row>
     <row r="25">
@@ -1839,166 +1843,162 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2026013</v>
+        <v>4925921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12059 Laura ADRIEN [3CY]</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3 Cycles [3CY]</t>
-        </is>
-      </c>
+          <t>Richard Archambault</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>567.131</v>
+        <v>682.222</v>
       </c>
       <c r="G25" t="n">
-        <v>31.05799999999999</v>
+        <v>146.149</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>88976</v>
+        <v>5070491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thomas Lokar &amp;#128058;</t>
+          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>571.562</v>
+        <v>718.255</v>
       </c>
       <c r="G26" t="n">
-        <v>35.48900000000003</v>
+        <v>238.318</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3937260</v>
+        <v>5238690</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Addict Shigyo</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Kjeld van der Lijke</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TBR Racing</t>
+        </is>
+      </c>
       <c r="F27" t="n">
-        <v>588.2910000000001</v>
+        <v>532.005</v>
       </c>
       <c r="G27" t="n">
-        <v>52.21800000000007</v>
+        <v>52.06799999999998</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>599299</v>
+        <v>6166908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>luigi kristensen</t>
+          <t>Cory Gross</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>600.14</v>
+        <v>577.551</v>
       </c>
       <c r="G28" t="n">
-        <v>64.06700000000001</v>
+        <v>88.73400000000004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>922347</v>
+        <v>6973606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YH. Tan</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[Ascenders]</t>
-        </is>
-      </c>
+          <t>Ch NAKA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>613.372</v>
+        <v>577.187</v>
       </c>
       <c r="G29" t="n">
-        <v>77.29899999999998</v>
+        <v>88.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4925921</v>
+        <v>7317487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Richard Archambault</t>
+          <t>B Goggin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>682.222</v>
+        <v>504.309</v>
       </c>
       <c r="G30" t="n">
-        <v>146.149</v>
+        <v>24.37200000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2013,46 +2013,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>558924</v>
+        <v>7319731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Robert Mairs</t>
+          <t>Ryan Baker</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>711.848</v>
+        <v>566.95</v>
       </c>
       <c r="G31" t="n">
-        <v>175.775</v>
+        <v>30.87700000000007</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4550173</v>
+        <v>7619023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Robert Kuramshin</t>
+          <t>Simone Batini</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>661.97</v>
+        <v>533.292</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>53.35500000000002</v>
       </c>
     </row>
     <row r="33">
@@ -2136,156 +2136,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4732668</v>
+        <v>15541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ekhi Congil</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PETA-Z</t>
-        </is>
-      </c>
+          <t>Landon Orr</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>577.035</v>
+        <v>1000.715</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>184.9060000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>722842</v>
+        <v>23014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>&amp;#129445; O  Gordinho Gal&amp;aacute;tico</t>
+          <t>Niels Pedersen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZTBR</t>
+          <t>BCKR</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>583.321</v>
+        <v>816.691</v>
       </c>
       <c r="G3" t="n">
-        <v>6.286000000000058</v>
+        <v>0.8820000000000618</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4585796</v>
+        <v>58527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jos Meijer CS030</t>
+          <t>Adrian Roebuck</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS030 </t>
+          <t>RollCo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>593.926</v>
+        <v>871.465</v>
       </c>
       <c r="G4" t="n">
-        <v>16.89100000000008</v>
+        <v>55.65600000000006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1557055</v>
+        <v>445221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerben @ridewithgerben </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CSG</t>
-        </is>
-      </c>
+          <t>Mitchell Bell</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>620.134</v>
+        <v>1847.978</v>
       </c>
       <c r="G5" t="n">
-        <v>43.09900000000005</v>
+        <v>1032.169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7250950</v>
+        <v>519022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Matthew Gleeson [TNP]</t>
+          <t xml:space="preserve">Johan Coppens </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>621.006</v>
+        <v>1882.2</v>
       </c>
       <c r="G6" t="n">
-        <v>43.971</v>
+        <v>1218.96</v>
       </c>
     </row>
     <row r="7">
@@ -2296,50 +2288,54 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1685325</v>
+        <v>722842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.B.Brantley  </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>&amp;#129445; O  Gordinho Gal&amp;aacute;tico</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ZTBR</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>647.712</v>
+        <v>583.321</v>
       </c>
       <c r="G7" t="n">
-        <v>70.67700000000002</v>
+        <v>6.286000000000058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4738957</v>
+        <v>904799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
+          <t>M.ike Stabler</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>663.24</v>
+        <v>1011.104</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>112.442</v>
       </c>
     </row>
     <row r="9">
@@ -2376,148 +2372,144 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7462775</v>
+        <v>1383579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diego Fontana </t>
+          <t>Sidney Luk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>679.798</v>
+        <v>1027.556</v>
       </c>
       <c r="G10" t="n">
-        <v>16.55799999999999</v>
+        <v>128.894</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>519022</v>
+        <v>1557055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan Coppens </t>
+          <t xml:space="preserve">Gerben @ridewithgerben </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1882.2</v>
+        <v>620.134</v>
       </c>
       <c r="G11" t="n">
-        <v>1218.96</v>
+        <v>43.09900000000005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7311595</v>
+        <v>1685325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jeremy Haddad</t>
+          <t xml:space="preserve">B.B.Brantley  </t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>815.809</v>
+        <v>647.712</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>70.67700000000002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23014</v>
+        <v>3043325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Niels Pedersen</t>
+          <t>Shane Quinn (DIRTy Rascals)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BCKR</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>816.691</v>
+        <v>1014.435</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8820000000000618</v>
+        <v>115.7729999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58527</v>
+        <v>3734234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Adrian Roebuck</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>T. Ohlrogge</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>871.465</v>
+        <v>950.9690000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>55.65600000000006</v>
+        <v>52.30700000000002</v>
       </c>
     </row>
     <row r="15">
@@ -2532,97 +2524,105 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15541</v>
+        <v>4533451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Landon Orr</t>
+          <t>R. Avigail</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>1000.715</v>
+        <v>1028.463</v>
       </c>
       <c r="G15" t="n">
-        <v>184.9060000000001</v>
+        <v>212.654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4533451</v>
+        <v>4534338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R. Avigail</t>
+          <t>Ben Amoz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>1028.463</v>
+        <v>904.752</v>
       </c>
       <c r="G16" t="n">
-        <v>212.654</v>
+        <v>6.089999999999918</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>445221</v>
+        <v>4585796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mitchell Bell</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Jos Meijer CS030</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS030 </t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>1847.978</v>
+        <v>593.926</v>
       </c>
       <c r="G17" t="n">
-        <v>1032.169</v>
+        <v>16.89100000000008</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7257803</v>
+        <v>4732668</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sam Schmarr</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Ekhi Congil</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PETA-Z</t>
+        </is>
+      </c>
       <c r="F18" t="n">
-        <v>898.662</v>
+        <v>577.035</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -2631,55 +2631,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4534338</v>
+        <v>4738957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ben Amoz</t>
+          <t>Markus Jochimsen</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>904.752</v>
+        <v>663.24</v>
       </c>
       <c r="G19" t="n">
-        <v>6.089999999999918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3734234</v>
+        <v>7250950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T. Ohlrogge</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Matthew Gleeson [TNP]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>950.9690000000001</v>
+        <v>621.006</v>
       </c>
       <c r="G20" t="n">
-        <v>52.30700000000002</v>
+        <v>43.971</v>
       </c>
     </row>
     <row r="21">
@@ -2690,42 +2694,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>904799</v>
+        <v>7257803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M.ike Stabler</t>
+          <t>Sam Schmarr</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>1011.104</v>
+        <v>898.662</v>
       </c>
       <c r="G21" t="n">
-        <v>112.442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3043325</v>
+        <v>7311595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shane Quinn (DIRTy Rascals)</t>
+          <t>Jeremy Haddad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2734,37 +2738,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1014.435</v>
+        <v>815.809</v>
       </c>
       <c r="G22" t="n">
-        <v>115.7729999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1383579</v>
+        <v>7462775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sidney Luk</t>
+          <t xml:space="preserve">Diego Fontana </t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1027.556</v>
+        <v>679.798</v>
       </c>
       <c r="G23" t="n">
-        <v>128.894</v>
+        <v>16.55799999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2805,9 +2809,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>time4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2744705</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jonathan Bush</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>708.636</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2818,76 +2891,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>zwift_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>pen</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_points</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>final_points</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>total_time</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>time1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>points1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>time2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>points2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>time3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>points3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>time4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>points4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A2" t="n">
+        <v>5070491</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2896,42 +2982,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Oliver Gaitan (TNP) </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Team Not Pogi</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>64</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>985.1990000000001</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>266.944</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>42</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>718.255</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>22</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1265626</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2940,124 +3033,145 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Alex Stuart r (BL13) </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>BL13</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>50</v>
-      </c>
-      <c r="F3" t="n">
-        <v>199.467</v>
       </c>
       <c r="G3" t="n">
         <v>199.467</v>
       </c>
       <c r="H3" t="n">
+        <v>199.467</v>
+      </c>
+      <c r="I3" t="n">
         <v>50</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1308320</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Luke Osborne [RWB eSports] </t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Team RWB</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>50</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>479.937</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>479.937</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>50</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4732668</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Ekhi Congil</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>PETA-Z</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>50</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>577.035</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>577.035</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>50</v>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2744705</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -3066,2811 +3180,3363 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jonathan Bush</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>708.636</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>708.636</v>
+      </c>
+      <c r="O6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7078446</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Ash.&amp;#127793;  Miles (ABR)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>ABR Cycle Team</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F7" t="n">
         <v>45</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G7" t="n">
         <v>225.328</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H7" t="n">
         <v>225.328</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I7" t="n">
         <v>45</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>79179</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Morten Andersen</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>#EDDK</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F8" t="n">
         <v>45</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G8" t="n">
         <v>487.635</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>487.635</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K8" t="n">
         <v>45</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>722842</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>&amp;#129445; O  Gordinho Gal&amp;aacute;tico</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>ZTBR</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F9" t="n">
         <v>45</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G9" t="n">
         <v>583.321</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>583.321</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M9" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1457528</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>William [ghost]</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F10" t="n">
         <v>42</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G10" t="n">
         <v>496.404</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>496.404</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K10" t="n">
         <v>42</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4585796</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Jos Meijer CS030</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">CS030 </t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F11" t="n">
         <v>42</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G11" t="n">
         <v>593.926</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>593.926</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M11" t="n">
         <v>42</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>684576</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Robbie Alunni</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Team Jane Fonda</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F12" t="n">
         <v>40</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G12" t="n">
         <v>322.48</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H12" t="n">
         <v>322.48</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I12" t="n">
         <v>40</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2344929</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Mitchell Stewart</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>BCC</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F13" t="n">
         <v>40</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G13" t="n">
         <v>502.271</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>502.271</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K13" t="n">
         <v>40</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1557055</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerben @ridewithgerben </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>CSG</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F14" t="n">
         <v>40</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G14" t="n">
         <v>620.134</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>620.134</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M14" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7317487</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>B Goggin</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
         <v>38</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G15" t="n">
         <v>504.309</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>504.309</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K15" t="n">
         <v>38</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7250950</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Matthew Gleeson [TNP]</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Team Not Pogi</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F16" t="n">
         <v>38</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G16" t="n">
         <v>621.006</v>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>621.006</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M16" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2100487</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>M Mike</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="F17" t="n">
         <v>36</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G17" t="n">
         <v>504.721</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>504.721</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K17" t="n">
         <v>36</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1685325</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">B.B.Brantley  </t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>36</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G18" t="n">
         <v>647.712</v>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>647.712</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M18" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2149546</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
         <v>34</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G19" t="n">
         <v>508.694</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>508.694</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K19" t="n">
         <v>34</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1857344</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Racing Ruub</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>The Watt Squad</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F20" t="n">
         <v>32</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G20" t="n">
         <v>513.434</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>513.434</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K20" t="n">
         <v>32</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5238690</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Kjeld van der Lijke</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>TBR Racing</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F21" t="n">
         <v>30</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G21" t="n">
         <v>532.005</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>532.005</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K21" t="n">
         <v>30</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7619023</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Simone Batini</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>28</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G22" t="n">
         <v>533.292</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>533.292</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K22" t="n">
         <v>28</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4390497</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Alex Hart (BL13)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>BL13</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F23" t="n">
         <v>26</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G23" t="n">
         <v>537.454</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>537.454</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K23" t="n">
         <v>26</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>909259</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Roland Nestler</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
         <v>24</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G24" t="n">
         <v>541.193</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>541.193</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K24" t="n">
         <v>24</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>990876</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">Pete Connor (TNP) </t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Team Not Pogi</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F25" t="n">
         <v>86</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G25" t="n">
         <v>812.973</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H25" t="n">
         <v>236.038</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I25" t="n">
         <v>50</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J25" t="n">
         <v>576.9349999999999</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K25" t="n">
         <v>36</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4500073</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Pieter de Meester</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
         <v>50</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G26" t="n">
         <v>488.817</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>488.817</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K26" t="n">
         <v>50</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4738957</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Markus Jochimsen</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
         <v>50</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G27" t="n">
         <v>663.24</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>663.24</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M27" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3081959</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Jomar Bjorge</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
         <v>45</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G28" t="n">
         <v>241.333</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H28" t="n">
         <v>241.333</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I28" t="n">
         <v>45</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2806376</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Daan Crombach</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>ZweetZ</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="F29" t="n">
         <v>45</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G29" t="n">
         <v>512.711</v>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>512.711</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K29" t="n">
         <v>45</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1376550</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">Scott  Adams (OTR TWSS) </t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>OTR Racing</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="F30" t="n">
         <v>45</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G30" t="n">
         <v>672.162</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>672.162</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M30" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>199053</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Trevor Connor (MGCC)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>MGCC</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="F31" t="n">
         <v>42</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G31" t="n">
         <v>241.356</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H31" t="n">
         <v>241.356</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I31" t="n">
         <v>42</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1048743</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Stephen Anderson</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
         <v>42</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G32" t="n">
         <v>518.052</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>518.052</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K32" t="n">
         <v>42</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7462775</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">Diego Fontana </t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
         <v>42</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G33" t="n">
         <v>679.798</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>679.798</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M33" t="n">
         <v>42</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>334292</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Eugene Klitenik [B2C2]</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
         <v>40</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G34" t="n">
         <v>255.848</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H34" t="n">
         <v>255.848</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I34" t="n">
         <v>40</v>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1627178</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Antonio Mateus</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>PTz</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F35" t="n">
         <v>40</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G35" t="n">
         <v>519.272</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>519.272</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K35" t="n">
         <v>40</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>519022</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">Johan Coppens </t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>The Watt Squad</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="F36" t="n">
         <v>40</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G36" t="n">
         <v>1882.2</v>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1882.2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M36" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1654998</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>jean sebastien vaast</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
         <v>38</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G37" t="n">
         <v>260.698</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H37" t="n">
         <v>260.698</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I37" t="n">
         <v>38</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4705264</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Scott Houck</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
         <v>38</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G38" t="n">
         <v>574.913</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>574.913</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K38" t="n">
         <v>38</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2747647</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Masahiko Uemura</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
         <v>36</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G39" t="n">
         <v>264.829</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H39" t="n">
         <v>264.829</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I39" t="n">
         <v>36</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>769731</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Steve Burns (Sussex Revolution VC - B)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>SRVC</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F40" t="n">
         <v>34</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G40" t="n">
         <v>290.585</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H40" t="n">
         <v>290.585</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I40" t="n">
         <v>34</v>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6973606</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Ch NAKA</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
         <v>34</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G41" t="n">
         <v>577.187</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>577.187</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K41" t="n">
         <v>34</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1281309</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
         <v>32</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G42" t="n">
         <v>373.381</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H42" t="n">
         <v>373.381</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I42" t="n">
         <v>32</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6166908</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Cory Gross</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
         <v>32</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G43" t="n">
         <v>577.551</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>577.551</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K43" t="n">
         <v>32</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2608736</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Daniel Pearson</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>SISU Racing</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="F44" t="n">
         <v>50</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G44" t="n">
         <v>260.425</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H44" t="n">
         <v>260.425</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I44" t="n">
         <v>50</v>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4177429</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t xml:space="preserve">F F </t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>50</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G45" t="n">
         <v>536.073</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>536.073</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K45" t="n">
         <v>50</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>7311595</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Jeremy Haddad</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>50</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G46" t="n">
         <v>815.809</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>815.809</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M46" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3148216</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Hide  Kaz0[SIMONE]</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="n">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
         <v>45</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G47" t="n">
         <v>260.888</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H47" t="n">
         <v>260.888</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I47" t="n">
         <v>45</v>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7319731</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Ryan Baker</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="n">
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
         <v>45</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G48" t="n">
         <v>566.95</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>566.95</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K48" t="n">
         <v>45</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>23014</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Niels Pedersen</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>BCKR</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="F49" t="n">
         <v>45</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G49" t="n">
         <v>816.691</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>816.691</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M49" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>659633</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Kris HSN</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="n">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
         <v>42</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G50" t="n">
         <v>287.815</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H50" t="n">
         <v>287.815</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I50" t="n">
         <v>42</v>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2026013</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>12059 Laura ADRIEN [3CY]</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>3 Cycles [3CY]</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="F51" t="n">
         <v>42</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G51" t="n">
         <v>567.131</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>567.131</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K51" t="n">
         <v>42</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>58527</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>Adrian Roebuck</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>RollCo</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="F52" t="n">
         <v>42</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G52" t="n">
         <v>871.465</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>871.465</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M52" t="n">
         <v>42</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2709880</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t xml:space="preserve"> T C</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
         <v>40</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G53" t="n">
         <v>298.541</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H53" t="n">
         <v>298.541</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I53" t="n">
         <v>40</v>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>88976</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Thomas Lokar &amp;#128058;</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>DIRT</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="F54" t="n">
         <v>40</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G54" t="n">
         <v>571.562</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>571.562</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K54" t="n">
         <v>40</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>15541</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Landon Orr</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
         <v>40</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G55" t="n">
         <v>1000.715</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
         <v>1000.715</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M55" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6912866</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Cathy Drozd</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
         <v>38</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G56" t="n">
         <v>302.218</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H56" t="n">
         <v>302.218</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I56" t="n">
         <v>38</v>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3937260</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Addict Shigyo</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
         <v>38</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G57" t="n">
         <v>588.2910000000001</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
         <v>588.2910000000001</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K57" t="n">
         <v>38</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4533451</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>R. Avigail</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
         <v>38</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G58" t="n">
         <v>1028.463</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>1028.463</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M58" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>599299</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>luigi kristensen</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
         <v>36</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G59" t="n">
         <v>600.14</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
         <v>600.14</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K59" t="n">
         <v>36</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>445221</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Mitchell Bell</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
         <v>36</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G60" t="n">
         <v>1847.978</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>1847.978</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M60" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>922347</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>YH. Tan</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>[Ascenders]</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="F61" t="n">
         <v>34</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G61" t="n">
         <v>613.372</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
         <v>613.372</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K61" t="n">
         <v>34</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4925921</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Richard Archambault</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
         <v>32</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G62" t="n">
         <v>682.222</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>682.222</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K62" t="n">
         <v>32</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>558924</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Robert Mairs</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
         <v>30</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G63" t="n">
         <v>711.848</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>711.848</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K63" t="n">
         <v>30</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1151116</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Michael Tandy (RHINO)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>RHINO</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="F64" t="n">
         <v>50</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G64" t="n">
         <v>280.771</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H64" t="n">
         <v>280.771</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I64" t="n">
         <v>50</v>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4550173</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Robert Kuramshin</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
         <v>50</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G65" t="n">
         <v>661.97</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>661.97</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K65" t="n">
         <v>50</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7257803</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>Sam Schmarr</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="n">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
         <v>50</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G66" t="n">
         <v>898.662</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
         <v>898.662</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M66" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7675581</v>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>Jesper Morsing</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="n">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
         <v>45</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G67" t="n">
         <v>326.363</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H67" t="n">
         <v>326.363</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I67" t="n">
         <v>45</v>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7663054</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Daniel Weare</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
         <v>45</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G68" t="n">
         <v>745.1559999999999</v>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
         <v>745.1559999999999</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K68" t="n">
         <v>45</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4534338</v>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Ben Amoz</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="n">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
         <v>45</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G69" t="n">
         <v>904.752</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
         <v>904.752</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M69" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>368051</v>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Andrew Speck BCC Astros</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>BCC Astros</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="F70" t="n">
         <v>42</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G70" t="n">
         <v>397.799</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H70" t="n">
         <v>397.799</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I70" t="n">
         <v>42</v>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3734234</v>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>T. Ohlrogge</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
         <v>42</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G71" t="n">
         <v>950.9690000000001</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
         <v>950.9690000000001</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M71" t="n">
         <v>42</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>116218</v>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Reidar Dahl</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="n">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
         <v>40</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G72" t="n">
         <v>420.161</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H72" t="n">
         <v>420.161</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I72" t="n">
         <v>40</v>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>904799</v>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>M.ike Stabler</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
         <v>40</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G73" t="n">
         <v>1011.104</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
         <v>1011.104</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M73" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>8165075</v>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t xml:space="preserve">kasie fox </t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="n">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
         <v>38</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G74" t="n">
         <v>470.545</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H74" t="n">
         <v>470.545</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I74" t="n">
         <v>38</v>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3043325</v>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Shane Quinn (DIRTy Rascals)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>DIRT</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="F75" t="n">
         <v>38</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G75" t="n">
         <v>1014.435</v>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
         <v>1014.435</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M75" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1383579</v>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Sidney Luk</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="n">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
         <v>36</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G76" t="n">
         <v>1027.556</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
         <v>1027.556</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M76" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>7501083</v>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Nellie Vrijburg</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="n">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
         <v>34</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G77" t="n">
         <v>1366.074</v>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
         <v>1366.074</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M77" t="n">
         <v>34</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/TheNextPeak/TheNextPeak__March_results.xlsx
+++ b/TheNextPeak/TheNextPeak__March_results.xlsx
@@ -472,175 +472,183 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116218</v>
+        <v>1265626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Reidar Dahl</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>420.161</v>
+        <v>199.467</v>
       </c>
       <c r="G2" t="n">
-        <v>139.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>199053</v>
+        <v>7078446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Trevor Connor (MGCC)</t>
+          <t>Ash.&amp;#127793;  Miles (ABR)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MGCC</t>
+          <t>ABR Cycle Team</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>241.356</v>
+        <v>225.328</v>
       </c>
       <c r="G3" t="n">
-        <v>5.317999999999984</v>
+        <v>25.86099999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>334292</v>
+        <v>5070491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Eugene Klitenik [B2C2]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>255.848</v>
+        <v>266.944</v>
       </c>
       <c r="G4" t="n">
-        <v>19.81</v>
+        <v>67.477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="C5" t="n">
-        <v>368051</v>
+        <v>684576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Andrew Speck BCC Astros</t>
+          <t>Robbie Alunni</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BCC Astros</t>
+          <t>Team Jane Fonda</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>397.799</v>
+        <v>322.48</v>
       </c>
       <c r="G5" t="n">
-        <v>117.028</v>
+        <v>123.013</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>659633</v>
+        <v>990876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kris HSN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>287.815</v>
+        <v>236.038</v>
       </c>
       <c r="G6" t="n">
-        <v>27.38999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>684576</v>
+        <v>3081959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Robbie Alunni</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Team Jane Fonda</t>
-        </is>
-      </c>
+          <t>Jomar Bjorge</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>322.48</v>
+        <v>241.333</v>
       </c>
       <c r="G7" t="n">
-        <v>123.013</v>
+        <v>5.294999999999987</v>
       </c>
     </row>
     <row r="8">
@@ -655,23 +663,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>769731</v>
+        <v>199053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Steve Burns (Sussex Revolution VC - B)</t>
+          <t>Trevor Connor (MGCC)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SRVC</t>
+          <t>MGCC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>290.585</v>
+        <v>241.356</v>
       </c>
       <c r="G8" t="n">
-        <v>54.54699999999997</v>
+        <v>5.317999999999984</v>
       </c>
     </row>
     <row r="9">
@@ -686,85 +694,73 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>990876</v>
+        <v>334292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pete Connor (TNP) </t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Eugene Klitenik [B2C2]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>236.038</v>
+        <v>255.848</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1151116</v>
+        <v>1654998</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Michael Tandy (RHINO)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>jean sebastien vaast</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>280.771</v>
+        <v>260.698</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>24.65999999999997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1265626</v>
+        <v>2747647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>BL13</t>
-        </is>
-      </c>
+          <t>Masahiko Uemura</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>199.467</v>
+        <v>264.829</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>28.791</v>
       </c>
     </row>
     <row r="12">
@@ -779,19 +775,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1281309</v>
+        <v>769731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Steve Burns (Sussex Revolution VC - B)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SRVC</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>373.381</v>
+        <v>290.585</v>
       </c>
       <c r="G12" t="n">
-        <v>137.343</v>
+        <v>54.54699999999997</v>
       </c>
     </row>
     <row r="13">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1654998</v>
+        <v>1281309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jean sebastien vaast</t>
+          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>260.698</v>
+        <v>373.381</v>
       </c>
       <c r="G13" t="n">
-        <v>24.65999999999997</v>
+        <v>137.343</v>
       </c>
     </row>
     <row r="14">
@@ -864,73 +864,73 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2709880</v>
+        <v>3148216</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> T C</t>
+          <t>Hide  Kaz0[SIMONE]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>298.541</v>
+        <v>260.888</v>
       </c>
       <c r="G15" t="n">
-        <v>38.11599999999999</v>
+        <v>0.4629999999999654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2747647</v>
+        <v>659633</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Masahiko Uemura</t>
+          <t>Kris HSN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>264.829</v>
+        <v>287.815</v>
       </c>
       <c r="G16" t="n">
-        <v>28.791</v>
+        <v>27.38999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3081959</v>
+        <v>2709880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jomar Bjorge</t>
+          <t xml:space="preserve"> T C</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>241.333</v>
+        <v>298.541</v>
       </c>
       <c r="G17" t="n">
-        <v>5.294999999999987</v>
+        <v>38.11599999999999</v>
       </c>
     </row>
     <row r="18">
@@ -945,56 +945,56 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3148216</v>
+        <v>6912866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hide  Kaz0[SIMONE]</t>
+          <t>Cathy Drozd</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>260.888</v>
+        <v>302.218</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4629999999999654</v>
+        <v>41.79300000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5070491</v>
+        <v>1151116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
+          <t>Michael Tandy (RHINO)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>266.944</v>
+        <v>280.771</v>
       </c>
       <c r="G19" t="n">
-        <v>67.477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1003,50 +1003,50 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6912866</v>
+        <v>7675581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cathy Drozd</t>
+          <t>Jesper Morsing</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>302.218</v>
+        <v>326.363</v>
       </c>
       <c r="G20" t="n">
-        <v>41.79300000000001</v>
+        <v>45.59199999999998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7078446</v>
+        <v>368051</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ash.&amp;#127793;  Miles (ABR)</t>
+          <t>Andrew Speck BCC Astros</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABR Cycle Team</t>
+          <t>BCC Astros</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>225.328</v>
+        <v>397.799</v>
       </c>
       <c r="G21" t="n">
-        <v>25.86099999999999</v>
+        <v>117.028</v>
       </c>
     </row>
     <row r="22">
@@ -1057,23 +1057,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7675581</v>
+        <v>116218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jesper Morsing</t>
+          <t>Reidar Dahl</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>326.363</v>
+        <v>420.161</v>
       </c>
       <c r="G22" t="n">
-        <v>45.59199999999998</v>
+        <v>139.39</v>
       </c>
     </row>
     <row r="23">
@@ -1166,108 +1166,116 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79179</v>
+        <v>1308320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Morten Andersen</t>
+          <t xml:space="preserve">Luke Osborne [RWB eSports] </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#EDDK</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>487.635</v>
+        <v>479.937</v>
       </c>
       <c r="G2" t="n">
-        <v>7.697999999999979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88976</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thomas Lokar &amp;#128058;</t>
+          <t>Morten Andersen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>#EDDK</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>571.562</v>
+        <v>487.635</v>
       </c>
       <c r="G3" t="n">
-        <v>35.48900000000003</v>
+        <v>7.697999999999979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>558924</v>
+        <v>1457528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Robert Mairs</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>William [ghost]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>711.848</v>
+        <v>496.404</v>
       </c>
       <c r="G4" t="n">
-        <v>175.775</v>
+        <v>16.46699999999998</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>599299</v>
+        <v>2344929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>luigi kristensen</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Mitchell Stewart</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BCC</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>600.14</v>
+        <v>502.271</v>
       </c>
       <c r="G5" t="n">
-        <v>64.06700000000001</v>
+        <v>22.334</v>
       </c>
     </row>
     <row r="6">
@@ -1278,112 +1286,112 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>909259</v>
+        <v>7317487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Roland Nestler</t>
+          <t>B Goggin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>541.193</v>
+        <v>504.309</v>
       </c>
       <c r="G6" t="n">
-        <v>61.25599999999997</v>
+        <v>24.37200000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>922347</v>
+        <v>2100487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YH. Tan</t>
+          <t>M Mike</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[Ascenders]</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>613.372</v>
+        <v>504.721</v>
       </c>
       <c r="G7" t="n">
-        <v>77.29899999999998</v>
+        <v>24.78399999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>990876</v>
+        <v>2149546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pete Connor (TNP) </t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>576.9349999999999</v>
+        <v>508.694</v>
       </c>
       <c r="G8" t="n">
-        <v>88.11799999999994</v>
+        <v>28.75700000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1048743</v>
+        <v>1857344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stephen Anderson</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Racing Ruub</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The Watt Squad</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>518.052</v>
+        <v>513.434</v>
       </c>
       <c r="G9" t="n">
-        <v>29.23500000000001</v>
+        <v>33.49699999999996</v>
       </c>
     </row>
     <row r="10">
@@ -1394,27 +1402,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1308320</v>
+        <v>5238690</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luke Osborne [RWB eSports] </t>
+          <t>Kjeld van der Lijke</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>TBR Racing</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>479.937</v>
+        <v>532.005</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>52.06799999999998</v>
       </c>
     </row>
     <row r="11">
@@ -1429,54 +1437,50 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1457528</v>
+        <v>7619023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>William [ghost]</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
-        </is>
-      </c>
+          <t>Simone Batini</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>496.404</v>
+        <v>533.292</v>
       </c>
       <c r="G11" t="n">
-        <v>16.46699999999998</v>
+        <v>53.35500000000002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1627178</v>
+        <v>4390497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Antonio Mateus</t>
+          <t>Alex Hart (BL13)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PTz</t>
+          <t>BL13</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>519.272</v>
+        <v>537.454</v>
       </c>
       <c r="G12" t="n">
-        <v>30.45500000000004</v>
+        <v>57.51699999999994</v>
       </c>
     </row>
     <row r="13">
@@ -1487,147 +1491,139 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1857344</v>
+        <v>909259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Racing Ruub</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>The Watt Squad</t>
-        </is>
-      </c>
+          <t>Roland Nestler</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>513.434</v>
+        <v>541.193</v>
       </c>
       <c r="G13" t="n">
-        <v>33.49699999999996</v>
+        <v>61.25599999999997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2026013</v>
+        <v>5070491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12059 Laura ADRIEN [3CY]</t>
+          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3 Cycles [3CY]</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>567.131</v>
+        <v>718.255</v>
       </c>
       <c r="G14" t="n">
-        <v>31.05799999999999</v>
+        <v>238.318</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2100487</v>
+        <v>4500073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M Mike</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
-        </is>
-      </c>
+          <t>Pieter de Meester</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>504.721</v>
+        <v>488.817</v>
       </c>
       <c r="G15" t="n">
-        <v>24.78399999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2149546</v>
+        <v>2806376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Daan Crombach</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ZweetZ</t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>508.694</v>
+        <v>512.711</v>
       </c>
       <c r="G16" t="n">
-        <v>28.75700000000001</v>
+        <v>23.89400000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2344929</v>
+        <v>1048743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mitchell Stewart</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BCC</t>
-        </is>
-      </c>
+          <t>Stephen Anderson</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>502.271</v>
+        <v>518.052</v>
       </c>
       <c r="G17" t="n">
-        <v>22.334</v>
+        <v>29.23500000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1642,112 +1638,108 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2806376</v>
+        <v>1627178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Daan Crombach</t>
+          <t>Antonio Mateus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ZweetZ</t>
+          <t>PTz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>512.711</v>
+        <v>519.272</v>
       </c>
       <c r="G18" t="n">
-        <v>23.89400000000001</v>
+        <v>30.45500000000004</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3937260</v>
+        <v>4705264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Addict Shigyo</t>
+          <t>Scott Houck</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>588.2910000000001</v>
+        <v>574.913</v>
       </c>
       <c r="G19" t="n">
-        <v>52.21800000000007</v>
+        <v>86.096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4177429</v>
+        <v>990876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>536.073</v>
+        <v>576.9349999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>88.11799999999994</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4390497</v>
+        <v>6973606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alex Hart (BL13)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BL13</t>
-        </is>
-      </c>
+          <t>Ch NAKA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>537.454</v>
+        <v>577.187</v>
       </c>
       <c r="G21" t="n">
-        <v>57.51699999999994</v>
+        <v>88.37</v>
       </c>
     </row>
     <row r="22">
@@ -1758,47 +1750,51 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4500073</v>
+        <v>6166908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pieter de Meester</t>
+          <t>Cory Gross</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>488.817</v>
+        <v>577.551</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>88.73400000000004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4550173</v>
+        <v>4177429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Robert Kuramshin</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t xml:space="preserve">F F </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
       <c r="F23" t="n">
-        <v>661.97</v>
+        <v>536.073</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1807,28 +1803,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4705264</v>
+        <v>7319731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Scott Houck</t>
+          <t>Ryan Baker</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>574.913</v>
+        <v>566.95</v>
       </c>
       <c r="G24" t="n">
-        <v>86.096</v>
+        <v>30.87700000000007</v>
       </c>
     </row>
     <row r="25">
@@ -1843,162 +1839,166 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4925921</v>
+        <v>2026013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Richard Archambault</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>12059 Laura ADRIEN [3CY]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3 Cycles [3CY]</t>
+        </is>
+      </c>
       <c r="F25" t="n">
-        <v>682.222</v>
+        <v>567.131</v>
       </c>
       <c r="G25" t="n">
-        <v>146.149</v>
+        <v>31.05799999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5070491</v>
+        <v>88976</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oliver Gaitan (TNP) </t>
+          <t>Thomas Lokar &amp;#128058;</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>718.255</v>
+        <v>571.562</v>
       </c>
       <c r="G26" t="n">
-        <v>238.318</v>
+        <v>35.48900000000003</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5238690</v>
+        <v>3937260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kjeld van der Lijke</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TBR Racing</t>
-        </is>
-      </c>
+          <t>Addict Shigyo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>532.005</v>
+        <v>588.2910000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>52.06799999999998</v>
+        <v>52.21800000000007</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6166908</v>
+        <v>599299</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cory Gross</t>
+          <t>luigi kristensen</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>577.551</v>
+        <v>600.14</v>
       </c>
       <c r="G28" t="n">
-        <v>88.73400000000004</v>
+        <v>64.06700000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6973606</v>
+        <v>922347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ch NAKA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>YH. Tan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[Ascenders]</t>
+        </is>
+      </c>
       <c r="F29" t="n">
-        <v>577.187</v>
+        <v>613.372</v>
       </c>
       <c r="G29" t="n">
-        <v>88.37</v>
+        <v>77.29899999999998</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7317487</v>
+        <v>4925921</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B Goggin</t>
+          <t>Richard Archambault</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>504.309</v>
+        <v>682.222</v>
       </c>
       <c r="G30" t="n">
-        <v>24.37200000000001</v>
+        <v>146.149</v>
       </c>
     </row>
     <row r="31">
@@ -2013,46 +2013,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7319731</v>
+        <v>558924</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ryan Baker</t>
+          <t>Robert Mairs</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>566.95</v>
+        <v>711.848</v>
       </c>
       <c r="G31" t="n">
-        <v>30.87700000000007</v>
+        <v>175.775</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7619023</v>
+        <v>4550173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Simone Batini</t>
+          <t>Robert Kuramshin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>533.292</v>
+        <v>661.97</v>
       </c>
       <c r="G32" t="n">
-        <v>53.35500000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2136,148 +2136,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15541</v>
+        <v>4732668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Landon Orr</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Ekhi Congil</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PETA-Z</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>1000.715</v>
+        <v>577.035</v>
       </c>
       <c r="G2" t="n">
-        <v>184.9060000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23014</v>
+        <v>722842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Niels Pedersen</t>
+          <t>&amp;#129445; O  Gordinho Gal&amp;aacute;tico</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCKR</t>
+          <t>ZTBR</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>816.691</v>
+        <v>583.321</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8820000000000618</v>
+        <v>6.286000000000058</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58527</v>
+        <v>4585796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adrian Roebuck</t>
+          <t>Jos Meijer CS030</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t xml:space="preserve">CS030 </t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>871.465</v>
+        <v>593.926</v>
       </c>
       <c r="G4" t="n">
-        <v>55.65600000000006</v>
+        <v>16.89100000000008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>445221</v>
+        <v>1557055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mitchell Bell</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t xml:space="preserve">Gerben @ridewithgerben </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSG</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>1847.978</v>
+        <v>620.134</v>
       </c>
       <c r="G5" t="n">
-        <v>1032.169</v>
+        <v>43.09900000000005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>519022</v>
+        <v>7250950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan Coppens </t>
+          <t>Matthew Gleeson [TNP]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1882.2</v>
+        <v>621.006</v>
       </c>
       <c r="G6" t="n">
-        <v>1218.96</v>
+        <v>43.971</v>
       </c>
     </row>
     <row r="7">
@@ -2288,54 +2296,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>722842</v>
+        <v>1685325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>&amp;#129445; O  Gordinho Gal&amp;aacute;tico</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ZTBR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">B.B.Brantley  </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>583.321</v>
+        <v>647.712</v>
       </c>
       <c r="G7" t="n">
-        <v>6.286000000000058</v>
+        <v>70.67700000000002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>904799</v>
+        <v>4738957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>M.ike Stabler</t>
+          <t>Markus Jochimsen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1011.104</v>
+        <v>663.24</v>
       </c>
       <c r="G8" t="n">
-        <v>112.442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2372,144 +2376,152 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1383579</v>
+        <v>7462775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sidney Luk</t>
+          <t xml:space="preserve">Diego Fontana </t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1027.556</v>
+        <v>679.798</v>
       </c>
       <c r="G10" t="n">
-        <v>128.894</v>
+        <v>16.55799999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1557055</v>
+        <v>519022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerben @ridewithgerben </t>
+          <t xml:space="preserve">Johan Coppens </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>620.134</v>
+        <v>1882.2</v>
       </c>
       <c r="G11" t="n">
-        <v>43.09900000000005</v>
+        <v>1218.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1685325</v>
+        <v>7311595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.B.Brantley  </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Jeremy Haddad</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>647.712</v>
+        <v>815.809</v>
       </c>
       <c r="G12" t="n">
-        <v>70.67700000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3043325</v>
+        <v>23014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shane Quinn (DIRTy Rascals)</t>
+          <t>Niels Pedersen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>BCKR</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1014.435</v>
+        <v>816.691</v>
       </c>
       <c r="G13" t="n">
-        <v>115.7729999999999</v>
+        <v>0.8820000000000618</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3734234</v>
+        <v>58527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T. Ohlrogge</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Adrian Roebuck</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F14" t="n">
-        <v>950.9690000000001</v>
+        <v>871.465</v>
       </c>
       <c r="G14" t="n">
-        <v>52.30700000000002</v>
+        <v>55.65600000000006</v>
       </c>
     </row>
     <row r="15">
@@ -2524,105 +2536,97 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4533451</v>
+        <v>15541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R. Avigail</t>
+          <t>Landon Orr</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>1028.463</v>
+        <v>1000.715</v>
       </c>
       <c r="G15" t="n">
-        <v>212.654</v>
+        <v>184.9060000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4534338</v>
+        <v>4533451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ben Amoz</t>
+          <t>R. Avigail</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>904.752</v>
+        <v>1028.463</v>
       </c>
       <c r="G16" t="n">
-        <v>6.089999999999918</v>
+        <v>212.654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4585796</v>
+        <v>445221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jos Meijer CS030</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS030 </t>
-        </is>
-      </c>
+          <t>Mitchell Bell</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>593.926</v>
+        <v>1847.978</v>
       </c>
       <c r="G17" t="n">
-        <v>16.89100000000008</v>
+        <v>1032.169</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4732668</v>
+        <v>7257803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ekhi Congil</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PETA-Z</t>
-        </is>
-      </c>
+          <t>Sam Schmarr</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>577.035</v>
+        <v>898.662</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -2631,59 +2635,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4738957</v>
+        <v>4534338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
+          <t>Ben Amoz</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>663.24</v>
+        <v>904.752</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>6.089999999999918</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7250950</v>
+        <v>3734234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Matthew Gleeson [TNP]</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>T. Ohlrogge</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>621.006</v>
+        <v>950.9690000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>43.971</v>
+        <v>52.30700000000002</v>
       </c>
     </row>
     <row r="21">
@@ -2694,42 +2694,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7257803</v>
+        <v>904799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sam Schmarr</t>
+          <t>M.ike Stabler</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>898.662</v>
+        <v>1011.104</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>112.442</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7311595</v>
+        <v>3043325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jeremy Haddad</t>
+          <t>Shane Quinn (DIRTy Rascals)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2738,37 +2738,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>815.809</v>
+        <v>1014.435</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>115.7729999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7462775</v>
+        <v>1383579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diego Fontana </t>
+          <t>Sidney Luk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>679.798</v>
+        <v>1027.556</v>
       </c>
       <c r="G23" t="n">
-        <v>16.55799999999999</v>
+        <v>128.894</v>
       </c>
     </row>
     <row r="24">
@@ -2809,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2861,23 +2861,583 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>745097</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>&amp;#9825; HJ [rsk]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>KZR</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>667.607</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1627974</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Daniel Pink</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bol</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>672.758</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.151000000000067</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4773510</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&amp;#29885;&amp;#39840; &amp;#173733;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>680.567</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.96000000000004</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>212786</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Erwin R</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TeamNL</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>694.602</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26.995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2744705</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Jonathan Bush</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>RHINO</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F6" t="n">
         <v>708.636</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="G6" t="n">
+        <v>41.029</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3023081</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A. NISHI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>712.654</v>
+      </c>
+      <c r="G7" t="n">
+        <v>45.04700000000003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1535238</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HITOSHI N</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>737.4450000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>69.83800000000008</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7008435</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VINCENT PEARSON [SVCC]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>778.5599999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>110.953</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>490524</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R D [SISU racing] </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SISU Racing</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>794.521</v>
+      </c>
+      <c r="G10" t="n">
+        <v>126.914</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>365813</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Craig McKenzie (TTL)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>835.479</v>
+      </c>
+      <c r="G11" t="n">
+        <v>167.8720000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>895306</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Justin Calta</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>862.249</v>
+      </c>
+      <c r="G12" t="n">
+        <v>194.6420000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5286078</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Felipe Serrano</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>884.438</v>
+      </c>
+      <c r="G13" t="n">
+        <v>216.831</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>435965</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>James Howman (Kernow)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>764.732</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6034009</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nguyen MS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>810.742</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46.00999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5393539</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Carsten Jensen</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>891.708</v>
+      </c>
+      <c r="G16" t="n">
+        <v>126.976</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6829675</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Anders Stagsted</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>916.1950000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>151.4630000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>718605</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>I Cant ride</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>947.14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>182.408</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1170121</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reona MTR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>952.837</v>
+      </c>
+      <c r="G19" t="n">
+        <v>188.105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>779638</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tiana Abel</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>956.909</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4651254</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Arjen De Jonge</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1032.996</v>
+      </c>
+      <c r="G21" t="n">
+        <v>76.0870000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1427961</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rob Koops</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>1165.053</v>
+      </c>
+      <c r="G22" t="n">
+        <v>208.1440000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2891,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,7 +3731,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2744705</v>
+        <v>745097</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -3185,19 +3745,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jonathan Bush</t>
+          <t>&amp;#9825; HJ [rsk]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>KZR</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>708.636</v>
+        <v>667.607</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
@@ -3212,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>708.636</v>
+        <v>667.607</v>
       </c>
       <c r="O6" t="n">
         <v>50</v>
@@ -3367,7 +3927,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1457528</v>
+        <v>1627974</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -3381,42 +3941,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>William [ghost]</t>
+          <t>Daniel Pink</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Bol</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>496.404</v>
+        <v>672.758</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
-        <v>496.404</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>672.758</v>
+      </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4585796</v>
+        <v>1457528</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -3425,38 +3985,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jos Meijer CS030</t>
+          <t>William [ghost]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS030 </t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>593.926</v>
+        <v>496.404</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>496.404</v>
+      </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>593.926</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
@@ -3465,7 +4025,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>684576</v>
+        <v>4585796</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3474,38 +4034,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Robbie Alunni</t>
+          <t>Jos Meijer CS030</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team Jane Fonda</t>
+          <t xml:space="preserve">CS030 </t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>322.48</v>
-      </c>
-      <c r="H12" t="n">
-        <v>322.48</v>
-      </c>
+        <v>593.926</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>593.926</v>
+      </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
@@ -3514,7 +4074,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2344929</v>
+        <v>4773510</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3523,47 +4083,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mitchell Stewart</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BCC</t>
-        </is>
-      </c>
+          <t>&amp;#29885;&amp;#39840; &amp;#173733;</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>502.271</v>
+        <v>680.567</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>502.271</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>680.567</v>
+      </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1557055</v>
+        <v>684576</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3572,38 +4128,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerben @ridewithgerben </t>
+          <t>Robbie Alunni</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Team Jane Fonda</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>620.134</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>322.48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>322.48</v>
+      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>620.134</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
@@ -3612,7 +4168,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7317487</v>
+        <v>2344929</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3626,25 +4182,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B Goggin</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Mitchell Stewart</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BCC</t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>504.309</v>
+        <v>502.271</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>504.309</v>
+        <v>502.271</v>
       </c>
       <c r="K15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -3657,7 +4217,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7250950</v>
+        <v>1557055</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3671,19 +4231,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Matthew Gleeson [TNP]</t>
+          <t xml:space="preserve">Gerben @ridewithgerben </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>621.006</v>
+        <v>620.134</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -3694,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>621.006</v>
+        <v>620.134</v>
       </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
@@ -3706,7 +4266,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2100487</v>
+        <v>212786</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3715,47 +4275,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M Mike</t>
+          <t>Erwin R</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>TeamNL</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>504.721</v>
+        <v>694.602</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>504.721</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>694.602</v>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1685325</v>
+        <v>7317487</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3764,34 +4324,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.B.Brantley  </t>
+          <t>B Goggin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>647.712</v>
+        <v>504.309</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>504.309</v>
+      </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>647.712</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
@@ -3800,7 +4360,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2149546</v>
+        <v>7250950</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3814,29 +4374,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Matthew Gleeson [TNP]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>508.694</v>
+        <v>621.006</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>508.694</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>34</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>621.006</v>
+      </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
@@ -3845,7 +4409,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1857344</v>
+        <v>2744705</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3854,47 +4418,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Racing Ruub</t>
+          <t>Jonathan Bush</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>513.434</v>
+        <v>708.636</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>513.434</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>708.636</v>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5238690</v>
+        <v>2100487</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3903,34 +4467,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kjeld van der Lijke</t>
+          <t>M Mike</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TBR Racing</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>532.005</v>
+        <v>504.721</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>532.005</v>
+        <v>504.721</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
@@ -3943,7 +4507,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7619023</v>
+        <v>1685325</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3952,34 +4516,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Simone Batini</t>
+          <t xml:space="preserve">B.B.Brantley  </t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>533.292</v>
+        <v>647.712</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>533.292</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>28</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>647.712</v>
+      </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
@@ -3988,7 +4552,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4390497</v>
+        <v>3023081</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3997,47 +4561,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Alex Hart (BL13)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>BL13</t>
-        </is>
-      </c>
+          <t>A. NISHI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>537.454</v>
+        <v>712.654</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>537.454</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>712.654</v>
+      </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>909259</v>
+        <v>2149546</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4046,30 +4606,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Roland Nestler</t>
+          <t>Olivier  Derquenne [cyt91] (ZLIT) *VM*5322 (Les Fragiles)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>541.193</v>
+        <v>508.694</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>541.193</v>
+        <v>508.694</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
@@ -4082,62 +4642,56 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>990876</v>
+        <v>1535238</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pete Connor (TNP) </t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>HITOSHI N</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>812.973</v>
-      </c>
-      <c r="H25" t="n">
-        <v>236.038</v>
-      </c>
+        <v>737.4450000000001</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J25" t="n">
-        <v>576.9349999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>737.4450000000001</v>
+      </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4500073</v>
+        <v>1857344</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4147,25 +4701,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pieter de Meester</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Racing Ruub</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>The Watt Squad</t>
+        </is>
+      </c>
       <c r="F26" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>488.817</v>
+        <v>513.434</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>488.817</v>
+        <v>513.434</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
@@ -4178,11 +4736,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4738957</v>
+        <v>7008435</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4192,15 +4750,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
+          <t>VINCENT PEARSON [SVCC]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>663.24</v>
+        <v>778.5599999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -4210,52 +4768,56 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>663.24</v>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>50</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>778.5599999999999</v>
+      </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3081959</v>
+        <v>5238690</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jomar Bjorge</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>Kjeld van der Lijke</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TBR Racing</t>
+        </is>
+      </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>241.333</v>
-      </c>
-      <c r="H28" t="n">
-        <v>241.333</v>
-      </c>
+        <v>532.005</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>45</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>532.005</v>
+      </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
@@ -4268,96 +4830,92 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2806376</v>
+        <v>490524</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Daan Crombach</t>
+          <t xml:space="preserve">R D [SISU racing] </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ZweetZ</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>512.711</v>
+        <v>794.521</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="n">
-        <v>512.711</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>794.521</v>
+      </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1376550</v>
+        <v>7619023</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scott  Adams (OTR TWSS) </t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>OTR Racing</t>
-        </is>
-      </c>
+          <t>Simone Batini</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>672.162</v>
+        <v>533.292</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>533.292</v>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>672.162</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
@@ -4366,39 +4924,33 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>199053</v>
+        <v>365813</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Trevor Connor (MGCC)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MGCC</t>
-        </is>
-      </c>
+          <t>Craig McKenzie (TTL)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>241.356</v>
-      </c>
-      <c r="H31" t="n">
-        <v>241.356</v>
-      </c>
+        <v>835.479</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
@@ -4408,46 +4960,52 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>835.479</v>
+      </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1048743</v>
+        <v>4390497</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Stephen Anderson</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Alex Hart (BL13)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G32" t="n">
-        <v>518.052</v>
+        <v>537.454</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>518.052</v>
+        <v>537.454</v>
       </c>
       <c r="K32" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
@@ -4460,29 +5018,33 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7462775</v>
+        <v>895306</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diego Fontana </t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>Justin Calta</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>679.798</v>
+        <v>862.249</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -4492,24 +5054,24 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>679.798</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>42</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>862.249</v>
+      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>334292</v>
+        <v>909259</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4519,25 +5081,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Eugene Klitenik [B2C2]</t>
+          <t>Roland Nestler</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>255.848</v>
-      </c>
-      <c r="H34" t="n">
-        <v>255.848</v>
-      </c>
+        <v>541.193</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>40</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>541.193</v>
+      </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
@@ -4550,11 +5112,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1627178</v>
+        <v>5286078</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4564,42 +5126,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Antonio Mateus</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PTz</t>
-        </is>
-      </c>
+          <t>Felipe Serrano</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>519.272</v>
+        <v>884.438</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="n">
-        <v>519.272</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>884.438</v>
+      </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>519022</v>
+        <v>990876</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4613,33 +5171,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johan Coppens </t>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="G36" t="n">
-        <v>1882.2</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>812.973</v>
+      </c>
+      <c r="H36" t="n">
+        <v>236.038</v>
+      </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="J36" t="n">
+        <v>576.9349999999999</v>
+      </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1882.2</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
@@ -4648,7 +5208,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1654998</v>
+        <v>4500073</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4657,30 +5217,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jean sebastien vaast</t>
+          <t>Pieter de Meester</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
-        <v>260.698</v>
-      </c>
-      <c r="H37" t="n">
-        <v>260.698</v>
-      </c>
+        <v>488.817</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>38</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>488.817</v>
+      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
@@ -4693,7 +5253,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4705264</v>
+        <v>4738957</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4707,29 +5267,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Scott Houck</t>
+          <t>Markus Jochimsen</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>574.913</v>
+        <v>663.24</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>574.913</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>38</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>663.24</v>
+      </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -4738,7 +5298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2747647</v>
+        <v>435965</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4752,21 +5312,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Masahiko Uemura</t>
+          <t>James Howman (Kernow)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
-        <v>264.829</v>
-      </c>
-      <c r="H39" t="n">
-        <v>264.829</v>
-      </c>
+        <v>764.732</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
@@ -4776,14 +5334,16 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>764.732</v>
+      </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>769731</v>
+        <v>3081959</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4797,25 +5357,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Steve Burns (Sussex Revolution VC - B)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>SRVC</t>
-        </is>
-      </c>
+          <t>Jomar Bjorge</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
-        <v>290.585</v>
+        <v>241.333</v>
       </c>
       <c r="H40" t="n">
-        <v>290.585</v>
+        <v>241.333</v>
       </c>
       <c r="I40" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
@@ -4832,7 +5388,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6973606</v>
+        <v>2806376</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4846,25 +5402,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ch NAKA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Daan Crombach</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ZweetZ</t>
+        </is>
+      </c>
       <c r="F41" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>577.187</v>
+        <v>512.711</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>577.187</v>
+        <v>512.711</v>
       </c>
       <c r="K41" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
@@ -4877,7 +5437,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1281309</v>
+        <v>1376550</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4891,29 +5451,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t xml:space="preserve">Scott  Adams (OTR TWSS) </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="F42" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G42" t="n">
-        <v>373.381</v>
-      </c>
-      <c r="H42" t="n">
-        <v>373.381</v>
-      </c>
+        <v>672.162</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>672.162</v>
+      </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
@@ -4922,7 +5486,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6166908</v>
+        <v>6034009</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4936,70 +5500,70 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cory Gross</t>
+          <t>Nguyen MS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G43" t="n">
-        <v>577.551</v>
+        <v>810.742</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="n">
-        <v>577.551</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>810.742</v>
+      </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2608736</v>
+        <v>199053</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Daniel Pearson</t>
+          <t>Trevor Connor (MGCC)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>MGCC</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>260.425</v>
+        <v>241.356</v>
       </c>
       <c r="H44" t="n">
-        <v>260.425</v>
+        <v>241.356</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
@@ -5016,43 +5580,39 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4177429</v>
+        <v>1048743</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
-        </is>
-      </c>
+          <t>Stephen Anderson</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G45" t="n">
-        <v>536.073</v>
+        <v>518.052</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>536.073</v>
+        <v>518.052</v>
       </c>
       <c r="K45" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
@@ -5065,33 +5625,29 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7311595</v>
+        <v>7462775</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jeremy Haddad</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Diego Fontana </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G46" t="n">
-        <v>815.809</v>
+        <v>679.798</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -5102,10 +5658,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>815.809</v>
+        <v>679.798</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
@@ -5114,35 +5670,33 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3148216</v>
+        <v>5393539</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hide  Kaz0[SIMONE]</t>
+          <t>Carsten Jensen</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G47" t="n">
-        <v>260.888</v>
-      </c>
-      <c r="H47" t="n">
-        <v>260.888</v>
-      </c>
+        <v>891.708</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
@@ -5152,46 +5706,48 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>891.708</v>
+      </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7319731</v>
+        <v>334292</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ryan Baker</t>
+          <t>Eugene Klitenik [B2C2]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G48" t="n">
-        <v>566.95</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>255.848</v>
+      </c>
+      <c r="H48" t="n">
+        <v>255.848</v>
+      </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>566.95</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
@@ -5204,47 +5760,47 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23014</v>
+        <v>1627178</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Niels Pedersen</t>
+          <t>Antonio Mateus</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BCKR</t>
+          <t>PTz</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G49" t="n">
-        <v>816.691</v>
+        <v>519.272</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>519.272</v>
+      </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>816.691</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
@@ -5253,35 +5809,33 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>659633</v>
+        <v>6829675</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kris HSN</t>
+          <t>Anders Stagsted</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G50" t="n">
-        <v>287.815</v>
-      </c>
-      <c r="H50" t="n">
-        <v>287.815</v>
-      </c>
+        <v>916.1950000000001</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
@@ -5291,54 +5845,56 @@
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>916.1950000000001</v>
+      </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2026013</v>
+        <v>519022</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12059 Laura ADRIEN [3CY]</t>
+          <t xml:space="preserve">Johan Coppens </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3 Cycles [3CY]</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G51" t="n">
-        <v>567.131</v>
+        <v>1882.2</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="n">
-        <v>567.131</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>42</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1882.2</v>
+      </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -5347,47 +5903,43 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58527</v>
+        <v>1654998</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Adrian Roebuck</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RollCo</t>
-        </is>
-      </c>
+          <t>jean sebastien vaast</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G52" t="n">
-        <v>871.465</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>260.698</v>
+      </c>
+      <c r="H52" t="n">
+        <v>260.698</v>
+      </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="n">
-        <v>871.465</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
@@ -5396,39 +5948,39 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2709880</v>
+        <v>4705264</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> T C</t>
+          <t>Scott Houck</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G53" t="n">
-        <v>298.541</v>
-      </c>
-      <c r="H53" t="n">
-        <v>298.541</v>
-      </c>
+        <v>574.913</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>40</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>574.913</v>
+      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
@@ -5441,92 +5993,88 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>88976</v>
+        <v>718605</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thomas Lokar &amp;#128058;</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>I Cant ride</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G54" t="n">
-        <v>571.562</v>
+        <v>947.14</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="n">
-        <v>571.562</v>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>947.14</v>
+      </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15541</v>
+        <v>2747647</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Landon Orr</t>
+          <t>Masahiko Uemura</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G55" t="n">
-        <v>1000.715</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>264.829</v>
+      </c>
+      <c r="H55" t="n">
+        <v>264.829</v>
+      </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="L55" t="n">
-        <v>1000.715</v>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -5535,35 +6083,33 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6912866</v>
+        <v>1170121</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cathy Drozd</t>
+          <t>Reona MTR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G56" t="n">
-        <v>302.218</v>
-      </c>
-      <c r="H56" t="n">
-        <v>302.218</v>
-      </c>
+        <v>952.837</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
@@ -5573,46 +6119,52 @@
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>952.837</v>
+      </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3937260</v>
+        <v>769731</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Addict Shigyo</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Steve Burns (Sussex Revolution VC - B)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SRVC</t>
+        </is>
+      </c>
       <c r="F57" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G57" t="n">
-        <v>588.2910000000001</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>290.585</v>
+      </c>
+      <c r="H57" t="n">
+        <v>290.585</v>
+      </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>588.2910000000001</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
@@ -5625,43 +6177,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4533451</v>
+        <v>6973606</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R. Avigail</t>
+          <t>Ch NAKA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G58" t="n">
-        <v>1028.463</v>
+        <v>577.187</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>577.187</v>
+      </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1028.463</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
@@ -5670,39 +6222,39 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>599299</v>
+        <v>1281309</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>luigi kristensen</t>
+          <t>Cl&amp;eacute;ment DUPONQ [PN]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G59" t="n">
-        <v>600.14</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>373.381</v>
+      </c>
+      <c r="H59" t="n">
+        <v>373.381</v>
+      </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>600.14</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
@@ -5715,43 +6267,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>445221</v>
+        <v>6166908</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mitchell Bell</t>
+          <t>Cory Gross</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>1847.978</v>
+        <v>577.551</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>577.551</v>
+      </c>
       <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1847.978</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
@@ -5760,7 +6312,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>922347</v>
+        <v>2608736</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5774,29 +6326,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>YH. Tan</t>
+          <t>Daniel Pearson</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[Ascenders]</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>613.372</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>260.425</v>
+      </c>
+      <c r="H61" t="n">
+        <v>260.425</v>
+      </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>613.372</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
@@ -5809,7 +6361,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4925921</v>
+        <v>4177429</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5823,25 +6375,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Richard Archambault</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t xml:space="preserve">F F </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
       <c r="F62" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>682.222</v>
+        <v>536.073</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>682.222</v>
+        <v>536.073</v>
       </c>
       <c r="K62" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
@@ -5854,7 +6410,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>558924</v>
+        <v>7311595</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5868,29 +6424,33 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Robert Mairs</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Jeremy Haddad</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F63" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>711.848</v>
+        <v>815.809</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="n">
-        <v>711.848</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
-        <v>30</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>815.809</v>
+      </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
@@ -5899,39 +6459,33 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1151116</v>
+        <v>779638</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Michael Tandy (RHINO)</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Tiana Abel</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>280.771</v>
-      </c>
-      <c r="H64" t="n">
-        <v>280.771</v>
-      </c>
+        <v>956.909</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
@@ -5941,46 +6495,48 @@
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>956.909</v>
+      </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4550173</v>
+        <v>3148216</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Robert Kuramshin</t>
+          <t>Hide  Kaz0[SIMONE]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G65" t="n">
-        <v>661.97</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>260.888</v>
+      </c>
+      <c r="H65" t="n">
+        <v>260.888</v>
+      </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>661.97</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
@@ -5993,11 +6549,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7257803</v>
+        <v>7319731</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6007,29 +6563,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sam Schmarr</t>
+          <t>Ryan Baker</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G66" t="n">
-        <v>898.662</v>
+        <v>566.95</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>566.95</v>
+      </c>
       <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>898.662</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -6038,11 +6594,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>7675581</v>
+        <v>23014</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6052,29 +6608,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Jesper Morsing</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Niels Pedersen</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BCKR</t>
+        </is>
+      </c>
       <c r="F67" t="n">
         <v>45</v>
       </c>
       <c r="G67" t="n">
-        <v>326.363</v>
-      </c>
-      <c r="H67" t="n">
-        <v>326.363</v>
-      </c>
+        <v>816.691</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>0</v>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>816.691</v>
+      </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
@@ -6083,21 +6643,21 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>7663054</v>
+        <v>4651254</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Daniel Weare</t>
+          <t>Arjen De Jonge</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -6105,66 +6665,66 @@
         <v>45</v>
       </c>
       <c r="G68" t="n">
-        <v>745.1559999999999</v>
+        <v>1032.996</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="n">
-        <v>745.1559999999999</v>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>1032.996</v>
+      </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4534338</v>
+        <v>659633</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ben Amoz</t>
+          <t>Kris HSN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G69" t="n">
-        <v>904.752</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>287.815</v>
+      </c>
+      <c r="H69" t="n">
+        <v>287.815</v>
+      </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
         <v>0</v>
       </c>
-      <c r="L69" t="n">
-        <v>904.752</v>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -6173,43 +6733,43 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>368051</v>
+        <v>2026013</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Andrew Speck BCC Astros</t>
+          <t>12059 Laura ADRIEN [3CY]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BCC Astros</t>
+          <t>3 Cycles [3CY]</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>42</v>
       </c>
       <c r="G70" t="n">
-        <v>397.799</v>
-      </c>
-      <c r="H70" t="n">
-        <v>397.799</v>
-      </c>
+        <v>567.131</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>567.131</v>
+      </c>
+      <c r="K70" t="n">
         <v>42</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="n">
-        <v>0</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
@@ -6222,29 +6782,33 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3734234</v>
+        <v>58527</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>T. Ohlrogge</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>Adrian Roebuck</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>42</v>
       </c>
       <c r="G71" t="n">
-        <v>950.9690000000001</v>
+        <v>871.465</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
@@ -6255,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>950.9690000000001</v>
+        <v>871.465</v>
       </c>
       <c r="M71" t="n">
         <v>42</v>
@@ -6267,35 +6831,33 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>116218</v>
+        <v>1427961</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Reidar Dahl</t>
+          <t>Rob Koops</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G72" t="n">
-        <v>420.161</v>
-      </c>
-      <c r="H72" t="n">
-        <v>420.161</v>
-      </c>
+        <v>1165.053</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
@@ -6305,28 +6867,30 @@
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>1165.053</v>
+      </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>904799</v>
+        <v>2709880</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M.ike Stabler</t>
+          <t xml:space="preserve"> T C</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -6334,21 +6898,21 @@
         <v>40</v>
       </c>
       <c r="G73" t="n">
-        <v>1011.104</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>298.541</v>
+      </c>
+      <c r="H73" t="n">
+        <v>298.541</v>
+      </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="n">
-        <v>1011.104</v>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
@@ -6357,39 +6921,43 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>8165075</v>
+        <v>88976</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">kasie fox </t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>Thomas Lokar &amp;#128058;</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F74" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G74" t="n">
-        <v>470.545</v>
-      </c>
-      <c r="H74" t="n">
-        <v>470.545</v>
-      </c>
+        <v>571.562</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>38</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>571.562</v>
+      </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
@@ -6402,33 +6970,29 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3043325</v>
+        <v>15541</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shane Quinn (DIRTy Rascals)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Landon Orr</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G75" t="n">
-        <v>1014.435</v>
+        <v>1000.715</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
@@ -6439,10 +7003,10 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1014.435</v>
+        <v>1000.715</v>
       </c>
       <c r="M75" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -6451,43 +7015,43 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1383579</v>
+        <v>6912866</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sidney Luk</t>
+          <t>Cathy Drozd</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G76" t="n">
-        <v>1027.556</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>302.218</v>
+      </c>
+      <c r="H76" t="n">
+        <v>302.218</v>
+      </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" t="n">
-        <v>1027.556</v>
-      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
@@ -6496,46 +7060,962 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>7501083</v>
+        <v>3937260</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Nellie Vrijburg</t>
+          <t>Addict Shigyo</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G77" t="n">
-        <v>1366.074</v>
+        <v>588.2910000000001</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>588.2910000000001</v>
+      </c>
       <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>1366.074</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4533451</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>R. Avigail</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>38</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1028.463</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1028.463</v>
+      </c>
+      <c r="M78" t="n">
+        <v>38</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>599299</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>luigi kristensen</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>36</v>
+      </c>
+      <c r="G79" t="n">
+        <v>600.14</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>600.14</v>
+      </c>
+      <c r="K79" t="n">
+        <v>36</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>445221</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mitchell Bell</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>36</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1847.978</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1847.978</v>
+      </c>
+      <c r="M80" t="n">
+        <v>36</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>922347</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>YH. Tan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>[Ascenders]</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>34</v>
+      </c>
+      <c r="G81" t="n">
+        <v>613.372</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>613.372</v>
+      </c>
+      <c r="K81" t="n">
+        <v>34</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4925921</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Richard Archambault</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>32</v>
+      </c>
+      <c r="G82" t="n">
+        <v>682.222</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>682.222</v>
+      </c>
+      <c r="K82" t="n">
+        <v>32</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>558924</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Robert Mairs</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>30</v>
+      </c>
+      <c r="G83" t="n">
+        <v>711.848</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>711.848</v>
+      </c>
+      <c r="K83" t="n">
+        <v>30</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1151116</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Michael Tandy (RHINO)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>50</v>
+      </c>
+      <c r="G84" t="n">
+        <v>280.771</v>
+      </c>
+      <c r="H84" t="n">
+        <v>280.771</v>
+      </c>
+      <c r="I84" t="n">
+        <v>50</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4550173</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Robert Kuramshin</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>50</v>
+      </c>
+      <c r="G85" t="n">
+        <v>661.97</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>661.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>50</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>7257803</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sam Schmarr</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>50</v>
+      </c>
+      <c r="G86" t="n">
+        <v>898.662</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>898.662</v>
+      </c>
+      <c r="M86" t="n">
+        <v>50</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>7675581</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jesper Morsing</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>45</v>
+      </c>
+      <c r="G87" t="n">
+        <v>326.363</v>
+      </c>
+      <c r="H87" t="n">
+        <v>326.363</v>
+      </c>
+      <c r="I87" t="n">
+        <v>45</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7663054</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Daniel Weare</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>45</v>
+      </c>
+      <c r="G88" t="n">
+        <v>745.1559999999999</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>745.1559999999999</v>
+      </c>
+      <c r="K88" t="n">
+        <v>45</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4534338</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ben Amoz</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>45</v>
+      </c>
+      <c r="G89" t="n">
+        <v>904.752</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>904.752</v>
+      </c>
+      <c r="M89" t="n">
+        <v>45</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>368051</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Andrew Speck BCC Astros</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>BCC Astros</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>42</v>
+      </c>
+      <c r="G90" t="n">
+        <v>397.799</v>
+      </c>
+      <c r="H90" t="n">
+        <v>397.799</v>
+      </c>
+      <c r="I90" t="n">
+        <v>42</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3734234</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>T. Ohlrogge</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>42</v>
+      </c>
+      <c r="G91" t="n">
+        <v>950.9690000000001</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>950.9690000000001</v>
+      </c>
+      <c r="M91" t="n">
+        <v>42</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>116218</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Reidar Dahl</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>40</v>
+      </c>
+      <c r="G92" t="n">
+        <v>420.161</v>
+      </c>
+      <c r="H92" t="n">
+        <v>420.161</v>
+      </c>
+      <c r="I92" t="n">
+        <v>40</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>904799</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>M.ike Stabler</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>40</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1011.104</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1011.104</v>
+      </c>
+      <c r="M93" t="n">
+        <v>40</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8165075</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kasie fox </t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>38</v>
+      </c>
+      <c r="G94" t="n">
+        <v>470.545</v>
+      </c>
+      <c r="H94" t="n">
+        <v>470.545</v>
+      </c>
+      <c r="I94" t="n">
+        <v>38</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3043325</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Shane Quinn (DIRTy Rascals)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>38</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1014.435</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1014.435</v>
+      </c>
+      <c r="M95" t="n">
+        <v>38</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1383579</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sidney Luk</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>36</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1027.556</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1027.556</v>
+      </c>
+      <c r="M96" t="n">
+        <v>36</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>7501083</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Nellie Vrijburg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>34</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1366.074</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1366.074</v>
+      </c>
+      <c r="M97" t="n">
+        <v>34</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
         <v>0</v>
       </c>
     </row>

--- a/TheNextPeak/TheNextPeak__March_results.xlsx
+++ b/TheNextPeak/TheNextPeak__March_results.xlsx
@@ -2809,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3263,19 +3263,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5393539</v>
+        <v>1106662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Carsten Jensen</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Geoffrey Gilbert9217</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>891.708</v>
+        <v>820.284</v>
       </c>
       <c r="G16" t="n">
-        <v>126.976</v>
+        <v>55.55200000000002</v>
       </c>
     </row>
     <row r="17">
@@ -3290,19 +3294,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6829675</v>
+        <v>1017356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anders Stagsted</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Nick Overkamp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WTOS</t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>916.1950000000001</v>
+        <v>880.395</v>
       </c>
       <c r="G17" t="n">
-        <v>151.4630000000001</v>
+        <v>115.663</v>
       </c>
     </row>
     <row r="18">
@@ -3317,19 +3325,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>718605</v>
+        <v>5393539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>I Cant ride</t>
+          <t>Carsten Jensen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>947.14</v>
+        <v>891.708</v>
       </c>
       <c r="G18" t="n">
-        <v>182.408</v>
+        <v>126.976</v>
       </c>
     </row>
     <row r="19">
@@ -3344,100 +3352,305 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1170121</v>
+        <v>6829675</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reona MTR</t>
+          <t>Anders Stagsted</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>952.837</v>
+        <v>916.1950000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>188.105</v>
+        <v>151.4630000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>779638</v>
+        <v>990876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tiana Abel</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>956.909</v>
+        <v>937.6799999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>172.948</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4651254</v>
+        <v>718605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arjen De Jonge</t>
+          <t>I Cant ride</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>1032.996</v>
+        <v>947.14</v>
       </c>
       <c r="G21" t="n">
-        <v>76.0870000000001</v>
+        <v>182.408</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1427961</v>
+        <v>1170121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rob Koops</t>
+          <t>Reona MTR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
+        <v>952.837</v>
+      </c>
+      <c r="G22" t="n">
+        <v>188.105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4177429</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F F </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>892.443</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3084196</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>902.825</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.38200000000006</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>779638</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tiana Abel</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>956.909</v>
+      </c>
+      <c r="G25" t="n">
+        <v>64.46600000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4651254</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Arjen De Jonge</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>1032.996</v>
+      </c>
+      <c r="G26" t="n">
+        <v>140.5530000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>560748</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Travis Lewis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1075.373</v>
+      </c>
+      <c r="G27" t="n">
+        <v>182.9300000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>458457</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bart Van De Ven8888</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>1134.879</v>
+      </c>
+      <c r="G28" t="n">
+        <v>242.4359999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1427961</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rob Koops</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
         <v>1165.053</v>
       </c>
-      <c r="G22" t="n">
-        <v>208.1440000000001</v>
+      <c r="G29" t="n">
+        <v>272.6100000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3451,7 +3664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5180,10 +5393,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G36" t="n">
-        <v>812.973</v>
+        <v>1750.653</v>
       </c>
       <c r="H36" t="n">
         <v>236.038</v>
@@ -5201,9 +5414,11 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>937.6799999999999</v>
+      </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -5307,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5670,7 +5885,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5393539</v>
+        <v>1106662</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5684,15 +5899,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Carsten Jensen</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Geoffrey Gilbert9217</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F47" t="n">
         <v>42</v>
       </c>
       <c r="G47" t="n">
-        <v>891.708</v>
+        <v>820.284</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -5707,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>891.708</v>
+        <v>820.284</v>
       </c>
       <c r="O47" t="n">
         <v>42</v>
@@ -5809,7 +6028,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6829675</v>
+        <v>1017356</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5823,15 +6042,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Anders Stagsted</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Nick Overkamp</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>WTOS</t>
+        </is>
+      </c>
       <c r="F50" t="n">
         <v>40</v>
       </c>
       <c r="G50" t="n">
-        <v>916.1950000000001</v>
+        <v>880.395</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -5846,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>916.1950000000001</v>
+        <v>880.395</v>
       </c>
       <c r="O50" t="n">
         <v>40</v>
@@ -5993,7 +6216,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>718605</v>
+        <v>5393539</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6007,7 +6230,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>I Cant ride</t>
+          <t>Carsten Jensen</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -6015,7 +6238,7 @@
         <v>38</v>
       </c>
       <c r="G54" t="n">
-        <v>947.14</v>
+        <v>891.708</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -6030,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>947.14</v>
+        <v>891.708</v>
       </c>
       <c r="O54" t="n">
         <v>38</v>
@@ -6083,7 +6306,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1170121</v>
+        <v>6829675</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6097,7 +6320,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Reona MTR</t>
+          <t>Anders Stagsted</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -6105,7 +6328,7 @@
         <v>36</v>
       </c>
       <c r="G56" t="n">
-        <v>952.837</v>
+        <v>916.1950000000001</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -6120,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>952.837</v>
+        <v>916.1950000000001</v>
       </c>
       <c r="O56" t="n">
         <v>36</v>
@@ -6312,39 +6535,33 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2608736</v>
+        <v>718605</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Daniel Pearson</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>I Cant ride</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>260.425</v>
-      </c>
-      <c r="H61" t="n">
-        <v>260.425</v>
-      </c>
+        <v>947.14</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
@@ -6354,63 +6571,61 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>947.14</v>
+      </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4177429</v>
+        <v>1170121</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
-        </is>
-      </c>
+          <t>Reona MTR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G62" t="n">
-        <v>536.073</v>
+        <v>952.837</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="n">
-        <v>536.073</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>952.837</v>
+      </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>7311595</v>
+        <v>4177429</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6424,42 +6639,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Jeremy Haddad</t>
+          <t xml:space="preserve">F F </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>815.809</v>
+        <v>1428.516</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>536.073</v>
+      </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>815.809</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>892.443</v>
+      </c>
+      <c r="O63" t="n">
         <v>50</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>779638</v>
+        <v>2608736</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6473,19 +6690,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tiana Abel</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>Daniel Pearson</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SISU Racing</t>
+        </is>
+      </c>
       <c r="F64" t="n">
         <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>956.909</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>260.425</v>
+      </c>
+      <c r="H64" t="n">
+        <v>260.425</v>
+      </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
@@ -6495,16 +6718,14 @@
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
-        <v>956.909</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3148216</v>
+        <v>7311595</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6518,29 +6739,33 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hide  Kaz0[SIMONE]</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>Jeremy Haddad</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F65" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G65" t="n">
-        <v>260.888</v>
-      </c>
-      <c r="H65" t="n">
-        <v>260.888</v>
-      </c>
+        <v>815.809</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>0</v>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>815.809</v>
+      </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
@@ -6549,7 +6774,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7319731</v>
+        <v>3148216</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6563,7 +6788,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ryan Baker</t>
+          <t>Hide  Kaz0[SIMONE]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -6571,17 +6796,17 @@
         <v>45</v>
       </c>
       <c r="G66" t="n">
-        <v>566.95</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>260.888</v>
+      </c>
+      <c r="H66" t="n">
+        <v>260.888</v>
+      </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>566.95</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
@@ -6594,7 +6819,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>23014</v>
+        <v>7319731</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6608,33 +6833,29 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Niels Pedersen</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BCKR</t>
-        </is>
-      </c>
+          <t>Ryan Baker</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
         <v>45</v>
       </c>
       <c r="G67" t="n">
-        <v>816.691</v>
+        <v>566.95</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>566.95</v>
+      </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>816.691</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
@@ -6643,7 +6864,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4651254</v>
+        <v>23014</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6657,15 +6878,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Arjen De Jonge</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Niels Pedersen</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BCKR</t>
+        </is>
+      </c>
       <c r="F68" t="n">
         <v>45</v>
       </c>
       <c r="G68" t="n">
-        <v>1032.996</v>
+        <v>816.691</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
@@ -6675,20 +6900,20 @@
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>816.691</v>
+      </c>
       <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1032.996</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>659633</v>
+        <v>3084196</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -6702,21 +6927,23 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kris HSN</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
-        <v>287.815</v>
-      </c>
-      <c r="H69" t="n">
-        <v>287.815</v>
-      </c>
+        <v>902.825</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
@@ -6726,14 +6953,16 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>902.825</v>
+      </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2026013</v>
+        <v>659633</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -6747,29 +6976,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12059 Laura ADRIEN [3CY]</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>3 Cycles [3CY]</t>
-        </is>
-      </c>
+          <t>Kris HSN</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
         <v>42</v>
       </c>
       <c r="G70" t="n">
-        <v>567.131</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>287.815</v>
+      </c>
+      <c r="H70" t="n">
+        <v>287.815</v>
+      </c>
       <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>567.131</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
@@ -6782,7 +7007,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58527</v>
+        <v>2026013</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6796,33 +7021,33 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Adrian Roebuck</t>
+          <t>12059 Laura ADRIEN [3CY]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RollCo</t>
+          <t>3 Cycles [3CY]</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>42</v>
       </c>
       <c r="G71" t="n">
-        <v>871.465</v>
+        <v>567.131</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>567.131</v>
+      </c>
       <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>871.465</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -6831,7 +7056,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1427961</v>
+        <v>58527</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6845,15 +7070,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Rob Koops</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>Adrian Roebuck</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RollCo</t>
+        </is>
+      </c>
       <c r="F72" t="n">
         <v>42</v>
       </c>
       <c r="G72" t="n">
-        <v>1165.053</v>
+        <v>871.465</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
@@ -6863,20 +7092,20 @@
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>871.465</v>
+      </c>
       <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1165.053</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2709880</v>
+        <v>779638</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6890,21 +7119,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> T C</t>
+          <t>Tiana Abel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G73" t="n">
-        <v>298.541</v>
-      </c>
-      <c r="H73" t="n">
-        <v>298.541</v>
-      </c>
+        <v>956.909</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
@@ -6914,14 +7141,16 @@
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>956.909</v>
+      </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>88976</v>
+        <v>2709880</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6935,29 +7164,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thomas Lokar &amp;#128058;</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> T C</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>40</v>
       </c>
       <c r="G74" t="n">
-        <v>571.562</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>298.541</v>
+      </c>
+      <c r="H74" t="n">
+        <v>298.541</v>
+      </c>
       <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>571.562</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
@@ -6970,7 +7195,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15541</v>
+        <v>88976</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6984,29 +7209,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Landon Orr</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>Thomas Lokar &amp;#128058;</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F75" t="n">
         <v>40</v>
       </c>
       <c r="G75" t="n">
-        <v>1000.715</v>
+        <v>571.562</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>571.562</v>
+      </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1000.715</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -7015,7 +7244,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6912866</v>
+        <v>15541</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -7029,29 +7258,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cathy Drozd</t>
+          <t>Landon Orr</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G76" t="n">
-        <v>302.218</v>
-      </c>
-      <c r="H76" t="n">
-        <v>302.218</v>
-      </c>
+        <v>1000.715</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>1000.715</v>
+      </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
@@ -7060,7 +7289,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3937260</v>
+        <v>4651254</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -7074,38 +7303,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Addict Shigyo</t>
+          <t>Arjen De Jonge</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G77" t="n">
-        <v>588.2910000000001</v>
+        <v>1032.996</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="n">
-        <v>588.2910000000001</v>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>1032.996</v>
+      </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4533451</v>
+        <v>6912866</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -7119,7 +7348,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R. Avigail</t>
+          <t>Cathy Drozd</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -7127,21 +7356,21 @@
         <v>38</v>
       </c>
       <c r="G78" t="n">
-        <v>1028.463</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>302.218</v>
+      </c>
+      <c r="H78" t="n">
+        <v>302.218</v>
+      </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="n">
-        <v>1028.463</v>
-      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
@@ -7150,7 +7379,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>599299</v>
+        <v>3937260</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -7164,25 +7393,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>luigi kristensen</t>
+          <t>Addict Shigyo</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G79" t="n">
-        <v>600.14</v>
+        <v>588.2910000000001</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>600.14</v>
+        <v>588.2910000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
@@ -7195,7 +7424,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>445221</v>
+        <v>4533451</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -7209,15 +7438,15 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mitchell Bell</t>
+          <t>R. Avigail</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G80" t="n">
-        <v>1847.978</v>
+        <v>1028.463</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
@@ -7228,10 +7457,10 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1847.978</v>
+        <v>1028.463</v>
       </c>
       <c r="M80" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
@@ -7240,7 +7469,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>922347</v>
+        <v>560748</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -7254,42 +7483,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>YH. Tan</t>
+          <t>Travis Lewis</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[Ascenders]</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G81" t="n">
-        <v>613.372</v>
+        <v>1075.373</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>0</v>
       </c>
-      <c r="J81" t="n">
-        <v>613.372</v>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>0</v>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>1075.373</v>
+      </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4925921</v>
+        <v>599299</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -7303,25 +7532,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Richard Archambault</t>
+          <t>luigi kristensen</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G82" t="n">
-        <v>682.222</v>
+        <v>600.14</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>682.222</v>
+        <v>600.14</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
@@ -7334,7 +7563,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>558924</v>
+        <v>458457</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -7348,78 +7577,74 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Robert Mairs</t>
+          <t>Bart Van De Ven8888</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G83" t="n">
-        <v>711.848</v>
+        <v>1134.879</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="n">
-        <v>711.848</v>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>1134.879</v>
+      </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1151116</v>
+        <v>445221</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Michael Tandy (RHINO)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RHINO</t>
-        </is>
-      </c>
+          <t>Mitchell Bell</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G84" t="n">
-        <v>280.771</v>
-      </c>
-      <c r="H84" t="n">
-        <v>280.771</v>
-      </c>
+        <v>1847.978</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>1847.978</v>
+      </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
@@ -7428,39 +7653,43 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4550173</v>
+        <v>922347</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Robert Kuramshin</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>YH. Tan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>[Ascenders]</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G85" t="n">
-        <v>661.97</v>
+        <v>613.372</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>661.97</v>
+        <v>613.372</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
@@ -7473,11 +7702,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7257803</v>
+        <v>1427961</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7487,15 +7716,15 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sam Schmarr</t>
+          <t>Rob Koops</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G86" t="n">
-        <v>898.662</v>
+        <v>1165.053</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
@@ -7505,24 +7734,24 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="n">
-        <v>898.662</v>
-      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>50</v>
-      </c>
-      <c r="N86" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1165.053</v>
+      </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7675581</v>
+        <v>4925921</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7532,25 +7761,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jesper Morsing</t>
+          <t>Richard Archambault</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G87" t="n">
-        <v>326.363</v>
-      </c>
-      <c r="H87" t="n">
-        <v>326.363</v>
-      </c>
+        <v>682.222</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>45</v>
-      </c>
-      <c r="J87" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>682.222</v>
+      </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
@@ -7563,39 +7792,39 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7663054</v>
+        <v>558924</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Daniel Weare</t>
+          <t>Robert Mairs</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G88" t="n">
-        <v>745.1559999999999</v>
+        <v>711.848</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>745.1559999999999</v>
+        <v>711.848</v>
       </c>
       <c r="K88" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
@@ -7608,7 +7837,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4534338</v>
+        <v>1151116</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7622,29 +7851,33 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ben Amoz</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>Michael Tandy (RHINO)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RHINO</t>
+        </is>
+      </c>
       <c r="F89" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G89" t="n">
-        <v>904.752</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>280.771</v>
+      </c>
+      <c r="H89" t="n">
+        <v>280.771</v>
+      </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="n">
-        <v>904.752</v>
-      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
@@ -7653,7 +7886,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>368051</v>
+        <v>4550173</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -7667,29 +7900,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Andrew Speck BCC Astros</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>BCC Astros</t>
-        </is>
-      </c>
+          <t>Robert Kuramshin</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G90" t="n">
-        <v>397.799</v>
-      </c>
-      <c r="H90" t="n">
-        <v>397.799</v>
-      </c>
+        <v>661.97</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>42</v>
-      </c>
-      <c r="J90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>661.97</v>
+      </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
@@ -7702,7 +7931,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3734234</v>
+        <v>7257803</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -7711,20 +7940,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>T. Ohlrogge</t>
+          <t>Sam Schmarr</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G91" t="n">
-        <v>950.9690000000001</v>
+        <v>898.662</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
@@ -7735,10 +7964,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>950.9690000000001</v>
+        <v>898.662</v>
       </c>
       <c r="M91" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
@@ -7747,7 +7976,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>116218</v>
+        <v>7675581</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -7756,26 +7985,26 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Reidar Dahl</t>
+          <t>Jesper Morsing</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G92" t="n">
-        <v>420.161</v>
+        <v>326.363</v>
       </c>
       <c r="H92" t="n">
-        <v>420.161</v>
+        <v>326.363</v>
       </c>
       <c r="I92" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
@@ -7792,7 +8021,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>904799</v>
+        <v>7663054</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -7806,29 +8035,29 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>M.ike Stabler</t>
+          <t>Daniel Weare</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G93" t="n">
-        <v>1011.104</v>
+        <v>745.1559999999999</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
         <v>0</v>
       </c>
-      <c r="J93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>745.1559999999999</v>
+      </c>
       <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>1011.104</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
@@ -7837,7 +8066,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>8165075</v>
+        <v>4534338</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -7851,29 +8080,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">kasie fox </t>
+          <t>Ben Amoz</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G94" t="n">
-        <v>470.545</v>
-      </c>
-      <c r="H94" t="n">
-        <v>470.545</v>
-      </c>
+        <v>904.752</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>904.752</v>
+      </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
@@ -7882,7 +8111,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3043325</v>
+        <v>368051</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -7896,33 +8125,33 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Shane Quinn (DIRTy Rascals)</t>
+          <t>Andrew Speck BCC Astros</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>BCC Astros</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G95" t="n">
-        <v>1014.435</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>397.799</v>
+      </c>
+      <c r="H95" t="n">
+        <v>397.799</v>
+      </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>0</v>
       </c>
-      <c r="L95" t="n">
-        <v>1014.435</v>
-      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
@@ -7931,7 +8160,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1383579</v>
+        <v>3734234</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -7945,15 +8174,15 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sidney Luk</t>
+          <t>T. Ohlrogge</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G96" t="n">
-        <v>1027.556</v>
+        <v>950.9690000000001</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
@@ -7964,10 +8193,10 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1027.556</v>
+        <v>950.9690000000001</v>
       </c>
       <c r="M96" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
@@ -7976,7 +8205,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>7501083</v>
+        <v>116218</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -7990,32 +8219,261 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Nellie Vrijburg</t>
+          <t>Reidar Dahl</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G97" t="n">
-        <v>1366.074</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
+        <v>420.161</v>
+      </c>
+      <c r="H97" t="n">
+        <v>420.161</v>
+      </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
         <v>0</v>
       </c>
-      <c r="L97" t="n">
-        <v>1366.074</v>
-      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>904799</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>M.ike Stabler</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>40</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1011.104</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1011.104</v>
+      </c>
+      <c r="M98" t="n">
+        <v>40</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8165075</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kasie fox </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>38</v>
+      </c>
+      <c r="G99" t="n">
+        <v>470.545</v>
+      </c>
+      <c r="H99" t="n">
+        <v>470.545</v>
+      </c>
+      <c r="I99" t="n">
+        <v>38</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3043325</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Shane Quinn (DIRTy Rascals)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>38</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1014.435</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1014.435</v>
+      </c>
+      <c r="M100" t="n">
+        <v>38</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1383579</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sidney Luk</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>36</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1027.556</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1027.556</v>
+      </c>
+      <c r="M101" t="n">
+        <v>36</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>7501083</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Nellie Vrijburg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>34</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1366.074</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1366.074</v>
+      </c>
+      <c r="M102" t="n">
+        <v>34</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
         <v>0</v>
       </c>
     </row>
